--- a/artfynd/A 19975-2026 artfynd.xlsx
+++ b/artfynd/A 19975-2026 artfynd.xlsx
@@ -1136,7 +1136,7 @@
         <v>133811611</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>133811779</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19975-2026 artfynd.xlsx
+++ b/artfynd/A 19975-2026 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133812103</v>
+        <v>133811611</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Noppikoski, Noppikoski, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492276</v>
+        <v>492183</v>
       </c>
       <c r="R2" t="n">
-        <v>6818262</v>
+        <v>6818231</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fl träd</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,53 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133811632</v>
+        <v>133811779</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Noppikoski, Noppikoski, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492183</v>
+        <v>492236</v>
       </c>
       <c r="R3" t="n">
-        <v>6818231</v>
+        <v>6818367</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fl träd</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +901,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1133,48 +1118,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133811611</v>
+        <v>133811552</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Noppikoski, Noppikoski, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492183</v>
+        <v>492173</v>
       </c>
       <c r="R6" t="n">
-        <v>6818231</v>
+        <v>6818152</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera träd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1357,48 +1352,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133811779</v>
+        <v>133812103</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Noppikoski, Noppikoski, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492236</v>
+        <v>492276</v>
       </c>
       <c r="R8" t="n">
-        <v>6818367</v>
+        <v>6818262</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Fl träd</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 19975-2026 artfynd.xlsx
+++ b/artfynd/A 19975-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 19975-2026 artfynd.xlsx
+++ b/artfynd/A 19975-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 19975-2026 artfynd.xlsx
+++ b/artfynd/A 19975-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133811611</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133811779</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133811700</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133812029</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133811552</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133811717</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,8 +1501,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133812103</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>